--- a/survey/surveytab.xlsx
+++ b/survey/surveytab.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t xml:space="preserve">Tree traversal</t>
   </si>
@@ -34,13 +34,19 @@
     <t xml:space="preserve">BFS</t>
   </si>
   <si>
-    <t xml:space="preserve">Benchmark</t>
+    <t xml:space="preserve">BFS Benchmark</t>
   </si>
   <si>
     <t xml:space="preserve">DFS</t>
   </si>
   <si>
-    <t xml:space="preserve">isultrametric issue</t>
+    <t xml:space="preserve">DFS Benchmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improvements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generator Benchmark</t>
   </si>
   <si>
     <t xml:space="preserve">R</t>
@@ -58,10 +64,18 @@
     <t xml:space="preserve">µ</t>
   </si>
   <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
     <t xml:space="preserve">ggtree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">castor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-order, 
+Post-order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get all distances to root/tip
+Or get tree traversal root to tip</t>
   </si>
   <si>
     <t xml:space="preserve">python</t>
@@ -96,6 +110,9 @@
   </si>
   <si>
     <t xml:space="preserve">toytree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tree not displaying</t>
   </si>
   <si>
     <t xml:space="preserve">Julia</t>
@@ -229,7 +246,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -242,15 +259,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -259,10 +272,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -389,7 +398,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -414,176 +423,183 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="2"/>
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>33</v>
-      </c>
+      <c r="A16" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>34</v>
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/survey/surveytab.xlsx
+++ b/survey/surveytab.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
   <si>
     <t xml:space="preserve">Tree traversal</t>
   </si>
@@ -92,6 +93,13 @@
 Post-order</t>
   </si>
   <si>
+    <t xml:space="preserve">level order uses 
+pop-from-front, 
+which is O(n) 
+but there is an
+ O(1) manual </t>
+  </si>
+  <si>
     <t xml:space="preserve">cogent3</t>
   </si>
   <si>
@@ -146,6 +154,66 @@
   </si>
   <si>
     <t xml:space="preserve">DFS=pre-/post-/in-order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL FN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">levelorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ultrametricity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCUMENTATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEARCH FOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">x*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is.ultrametric </t>
+  </si>
+  <si>
+    <t xml:space="preserve">get_all_distances_to_root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glossary → preorder_node_iter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">find_clades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traverse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traversal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ok =&gt; GIT SHOWS THAT THERE ARE NATIVE EQUIVALENTS TO THOSE FUNCTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tree.postord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*found no native function but haven’t coded equivalent yet</t>
   </si>
 </sst>
 </file>
@@ -155,7 +223,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -197,6 +265,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <u val="single"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -246,7 +322,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -272,6 +348,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -471,7 +559,7 @@
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
@@ -487,7 +575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -500,11 +588,13 @@
       <c r="E6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="2"/>
+      <c r="G6" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
@@ -516,10 +606,10 @@
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>21</v>
@@ -528,65 +618,65 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -594,12 +684,12 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -611,4 +701,218 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="G2" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>